--- a/space-battleship/config_excel/crew.xlsx
+++ b/space-battleship/config_excel/crew.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crew" sheetId="1" r:id="R369a980d175a42d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crew" sheetId="1" r:id="R63612b65409a4acf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -332,6 +332,12 @@
       <x:c r="L1" s="4" t="str">
         <x:v>defaultTargetId</x:v>
       </x:c>
+      <x:c r="M1" t="str">
+        <x:v>baseExp</x:v>
+      </x:c>
+      <x:c r="N1" t="str">
+        <x:v>expGrowth</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="55" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -369,6 +375,12 @@
       </x:c>
       <x:c r="L2" s="6" t="str">
         <x:v>默认目标ID，岗位非空时填写</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>升级基础经验</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>每级升级经验增长率</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
@@ -384,6 +396,12 @@
       <x:c r="J3" s="2" t="str"/>
       <x:c r="K3" s="2" t="str"/>
       <x:c r="L3" s="2" t="str"/>
+      <x:c r="M3" t="str">
+        <x:v>从1级升2级所需经验</x:v>
+      </x:c>
+      <x:c r="N3" t="str">
+        <x:v>0.2表示每级增长20%</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -413,13 +431,19 @@
       <x:c r="I4" s="7" t="str"/>
       <x:c r="J4" s="7" t="inlineStr">
         <x:is>
-          <x:t>crew/navigator</x:t>
+          <x:t xml:space="preserve">crew/navigator</x:t>
         </x:is>
       </x:c>
       <x:c r="K4" s="7" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L4" s="7" t="str"/>
+      <x:c r="M4" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N4" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
       <x:c r="A5" s="7" t="str">
@@ -449,13 +473,19 @@
       <x:c r="I5" s="7" t="str"/>
       <x:c r="J5" s="7" t="inlineStr">
         <x:is>
-          <x:t>crew/engineer</x:t>
+          <x:t xml:space="preserve">crew/engineer</x:t>
         </x:is>
       </x:c>
       <x:c r="K5" s="7" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L5" s="7" t="str"/>
+      <x:c r="M5" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N5" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
       <x:c r="A6" s="7" t="str">
@@ -485,33 +515,39 @@
       <x:c r="I6" s="7" t="str"/>
       <x:c r="J6" s="7" t="inlineStr">
         <x:is>
-          <x:t>crew/researcher</x:t>
+          <x:t xml:space="preserve">crew/researcher</x:t>
         </x:is>
       </x:c>
       <x:c r="K6" s="7" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L6" s="7" t="str"/>
+      <x:c r="M6" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N6" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
       <x:c r="A7" s="7" t="inlineStr">
         <x:is>
-          <x:t>crew_04</x:t>
+          <x:t xml:space="preserve">crew_04</x:t>
         </x:is>
       </x:c>
       <x:c r="B7" s="7" t="inlineStr">
         <x:is>
-          <x:t>船员04</x:t>
+          <x:t xml:space="preserve">船员04</x:t>
         </x:is>
       </x:c>
       <x:c r="C7" s="7" t="inlineStr">
         <x:is>
-          <x:t>无固定职务，可自由分配到各游戏系统。</x:t>
+          <x:t xml:space="preserve">无固定职务，可自由分配到各游戏系统。</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" s="7" t="inlineStr">
         <x:is>
-          <x:t>res://assets/ui/crew.svg</x:t>
+          <x:t xml:space="preserve">res://assets/ui/crew.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="E7" s="7">
@@ -525,39 +561,45 @@
       </x:c>
       <x:c r="H7" s="7" t="inlineStr">
         <x:is>
-          <x:t>normal</x:t>
+          <x:t xml:space="preserve">normal</x:t>
         </x:is>
       </x:c>
       <x:c r="I7" s="7"/>
       <x:c r="J7" s="7" t="inlineStr">
         <x:is>
-          <x:t>crew/crew_04</x:t>
+          <x:t xml:space="preserve">crew/crew_04</x:t>
         </x:is>
       </x:c>
       <x:c r="K7" s="7">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="7"/>
+      <x:c r="M7" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N7" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
       <x:c r="A8" s="7" t="inlineStr">
         <x:is>
-          <x:t>crew_05</x:t>
+          <x:t xml:space="preserve">crew_05</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" s="7" t="inlineStr">
         <x:is>
-          <x:t>船员05</x:t>
+          <x:t xml:space="preserve">船员05</x:t>
         </x:is>
       </x:c>
       <x:c r="C8" s="7" t="inlineStr">
         <x:is>
-          <x:t>无固定职务，可自由分配到各游戏系统。</x:t>
+          <x:t xml:space="preserve">无固定职务，可自由分配到各游戏系统。</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" s="7" t="inlineStr">
         <x:is>
-          <x:t>res://assets/ui/crew.svg</x:t>
+          <x:t xml:space="preserve">res://assets/ui/crew.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="E8" s="7">
@@ -571,39 +613,45 @@
       </x:c>
       <x:c r="H8" s="7" t="inlineStr">
         <x:is>
-          <x:t>normal</x:t>
+          <x:t xml:space="preserve">normal</x:t>
         </x:is>
       </x:c>
       <x:c r="I8" s="7"/>
       <x:c r="J8" s="7" t="inlineStr">
         <x:is>
-          <x:t>crew/crew_05</x:t>
+          <x:t xml:space="preserve">crew/crew_05</x:t>
         </x:is>
       </x:c>
       <x:c r="K8" s="7">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L8" s="7"/>
+      <x:c r="M8" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N8" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
       <x:c r="A9" s="7" t="inlineStr">
         <x:is>
-          <x:t>crew_06</x:t>
+          <x:t xml:space="preserve">crew_06</x:t>
         </x:is>
       </x:c>
       <x:c r="B9" s="7" t="inlineStr">
         <x:is>
-          <x:t>船员06</x:t>
+          <x:t xml:space="preserve">船员06</x:t>
         </x:is>
       </x:c>
       <x:c r="C9" s="7" t="inlineStr">
         <x:is>
-          <x:t>无固定职务，可自由分配到各游戏系统。</x:t>
+          <x:t xml:space="preserve">无固定职务，可自由分配到各游戏系统。</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" s="7" t="inlineStr">
         <x:is>
-          <x:t>res://assets/ui/crew.svg</x:t>
+          <x:t xml:space="preserve">res://assets/ui/crew.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" s="7">
@@ -617,19 +665,25 @@
       </x:c>
       <x:c r="H9" s="7" t="inlineStr">
         <x:is>
-          <x:t>normal</x:t>
+          <x:t xml:space="preserve">normal</x:t>
         </x:is>
       </x:c>
       <x:c r="I9" s="7"/>
       <x:c r="J9" s="7" t="inlineStr">
         <x:is>
-          <x:t>crew/crew_06</x:t>
+          <x:t xml:space="preserve">crew/crew_06</x:t>
         </x:is>
       </x:c>
       <x:c r="K9" s="7">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L9" s="7"/>
+      <x:c r="M9" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N9" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
